--- a/tame_output/ON/bt/strategyON_20240304.xlsx
+++ b/tame_output/ON/bt/strategyON_20240304.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.36402723556366</v>
+        <v>3.364027235563659</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>0.792789870126093</v>
+        <v>0.7928896385195343</v>
       </c>
       <c r="E1892" t="n">
-        <v>3.496383076248061</v>
+        <v>3.496422983605438</v>
       </c>
       <c r="F1892" t="n">
-        <v>1.649461728671108</v>
+        <v>1.649996644873574</v>
       </c>
       <c r="G1892" t="n">
-        <v>4.169300589714036</v>
+        <v>4.169621539435516</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240304.xlsx
+++ b/tame_output/ON/bt/strategyON_20240304.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-82.3%</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-26.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.364027235563659</v>
+        <v>3.36402723556366</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>0.7928896385195343</v>
+        <v>0.7943996080675013</v>
       </c>
       <c r="E1892" t="n">
-        <v>3.496422983605438</v>
+        <v>3.497026971424624</v>
       </c>
       <c r="F1892" t="n">
-        <v>1.649996644873574</v>
+        <v>1.650070760011954</v>
       </c>
       <c r="G1892" t="n">
-        <v>4.169621539435516</v>
+        <v>4.169666008518544</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240304.xlsx
+++ b/tame_output/ON/bt/strategyON_20240304.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>489.6%</t>
+          <t>485.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-107.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-36.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-59.0%</t>
+          <t>-67.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-34.1%</t>
         </is>
       </c>
     </row>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.36402723556366</v>
+        <v>3.364027235563659</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>0.7943996080675013</v>
+        <v>0.541106992870301</v>
       </c>
       <c r="E1892" t="n">
-        <v>3.497026971424624</v>
+        <v>3.395709925345744</v>
       </c>
       <c r="F1892" t="n">
-        <v>1.650070760011954</v>
+        <v>1.565246353987234</v>
       </c>
       <c r="G1892" t="n">
-        <v>4.169666008518544</v>
+        <v>4.118771364903711</v>
       </c>
     </row>
   </sheetData>
